--- a/datos/Semana30.xlsx
+++ b/datos/Semana30.xlsx
@@ -234,9 +234,6 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -263,6 +260,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,549 +556,549 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>46223</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>10033797</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>20018772</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>46223</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>10033798</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>20018775</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>46223</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>10033684</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>20018724</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>46223</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>46223</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>10032110</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>20017352</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="6"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>46223</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>10033799</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>20018776</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>46223</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>10033695</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>20018396</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="8"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>46223</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>10032447</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>20017635</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="8"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>46224</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>10032275</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>20017321</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>46224</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>10033794</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>20018771</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>46224</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>10032110</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>20017352</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="6"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>46225</v>
       </c>
-      <c r="B14" s="7">
-        <v>10032110</v>
-      </c>
-      <c r="C14" s="7">
-        <v>20017352</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="6">
+        <v>10033833</v>
+      </c>
+      <c r="C14" s="6">
+        <v>20018772</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>46225</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>10033797</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>20018772</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="8"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>46225</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>10033793</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>20018770</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>46226</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>10033749</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>20018399</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="E17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="8"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>46226</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>10033795</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>20018768</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="E18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="8"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>46226</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="E19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="8"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>46226</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>10033590</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>20018650</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="8"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>46227</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <v>10032595</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="6">
         <v>20017730</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="8"/>
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>46227</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="6">
         <v>10032598</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="6">
         <v>20017732</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="8"/>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>46227</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="6">
         <v>10032761</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="6">
         <v>20017781</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="8"/>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>46227</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="6">
         <v>10032446</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="6">
         <v>20014753</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="8"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>46228</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <v>10033796</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <v>20018777</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="4" t="s">
+      <c r="E25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>46228</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <v>10032288</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="6">
         <v>20017547</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>46229</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>10032286</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>20017545</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="E27" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="7" t="s">
         <v>44</v>
       </c>
     </row>
